--- a/sources/devil_step6b.xlsx
+++ b/sources/devil_step6b.xlsx
@@ -3721,7 +3721,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">

--- a/sources/devil_step6b.xlsx
+++ b/sources/devil_step6b.xlsx
@@ -733,6 +733,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>d45bec05-7204-4250-b59f-10fc5a9777d7</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>d45bec05-7204-4250-b59f-10fc5a9777d7</t>
@@ -780,6 +785,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>17795a91-f2dd-40be-9ae8-c1cac544dbd8</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>17795a91-f2dd-40be-9ae8-c1cac544dbd8</t>
@@ -825,6 +835,11 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>6cb3e0a1-740e-4fe0-abcb-9e9234259fe0</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -3926,6 +3941,11 @@
       <c r="K68" t="inlineStr">
         <is>
           <t>hhhhmmLhmm</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>f5b8d288-963e-48b0-91a0-9547d3e2d9cf</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
